--- a/filesystem/Finance/Financials/Bramwell_FY2025_standalone.xlsx
+++ b/filesystem/Finance/Financials/Bramwell_FY2025_standalone.xlsx
@@ -223,7 +223,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -486,11 +486,69 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -668,6 +726,10 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1113,14 +1175,6 @@
           <t>Revenue by Bramwell-Origin Client</t>
         </is>
       </c>
-      <c r="B1" s="36" t="n"/>
-      <c r="C1" s="36" t="n"/>
-      <c r="D1" s="36" t="n"/>
-      <c r="E1" s="36" t="n"/>
-      <c r="F1" s="36" t="n"/>
-      <c r="G1" s="36" t="n"/>
-      <c r="H1" s="36" t="n"/>
-      <c r="I1" s="36" t="n"/>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="37" t="inlineStr">
@@ -1128,14 +1182,14 @@
           <t>Currency: USD, whole dollars. Q3 revenue is presented on a whole-quarter basis; the July–August portion is pre-close (Bramwell as an independent entity) and the September portion is post-close (Bramwell operating as a Thornfield subsidiary).</t>
         </is>
       </c>
-      <c r="B2" s="38" t="n"/>
-      <c r="C2" s="38" t="n"/>
-      <c r="D2" s="38" t="n"/>
-      <c r="E2" s="38" t="n"/>
-      <c r="F2" s="38" t="n"/>
-      <c r="G2" s="38" t="n"/>
-      <c r="H2" s="38" t="n"/>
-      <c r="I2" s="38" t="n"/>
+      <c r="B2" s="69" t="n"/>
+      <c r="C2" s="69" t="n"/>
+      <c r="D2" s="69" t="n"/>
+      <c r="E2" s="69" t="n"/>
+      <c r="F2" s="69" t="n"/>
+      <c r="G2" s="69" t="n"/>
+      <c r="H2" s="69" t="n"/>
+      <c r="I2" s="69" t="n"/>
     </row>
     <row r="3" ht="12" customHeight="1"/>
     <row r="4" ht="42" customHeight="1">
@@ -1453,7 +1507,7 @@
       </c>
       <c r="C13" s="42" t="inlineStr">
         <is>
-          <t>Pemberton Genetics</t>
+          <t>Foxhaven Genomic Analytics</t>
         </is>
       </c>
       <c r="D13" s="43" t="n">
@@ -1581,7 +1635,7 @@
       </c>
       <c r="C17" s="42" t="inlineStr">
         <is>
-          <t>Whitcombe Diagnostics</t>
+          <t>Kettlewell Diagnostics</t>
         </is>
       </c>
       <c r="D17" s="43" t="n">
@@ -1613,7 +1667,7 @@
       </c>
       <c r="C18" s="46" t="inlineStr">
         <is>
-          <t>Bramford Optics</t>
+          <t>Norcross Genomic Systems</t>
         </is>
       </c>
       <c r="D18" s="47" t="n">
@@ -1830,8 +1884,8 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B25" s="50" t="n"/>
-      <c r="C25" s="50" t="n"/>
+      <c r="B25" s="70" t="n"/>
+      <c r="C25" s="70" t="n"/>
       <c r="D25" s="51" t="n">
         <v>991167</v>
       </c>
@@ -1855,14 +1909,6 @@
           <t>Row count: 20 Bramwell-origin client accounts.</t>
         </is>
       </c>
-      <c r="B27" s="53" t="n"/>
-      <c r="C27" s="53" t="n"/>
-      <c r="D27" s="53" t="n"/>
-      <c r="E27" s="53" t="n"/>
-      <c r="F27" s="53" t="n"/>
-      <c r="G27" s="53" t="n"/>
-      <c r="H27" s="53" t="n"/>
-      <c r="I27" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1894,7 +1940,6 @@
           <t>FY2025 Totals — Bramwell Standalone</t>
         </is>
       </c>
-      <c r="B1" s="36" t="n"/>
     </row>
     <row r="2" ht="14" customHeight="1"/>
     <row r="3" ht="26" customHeight="1">
@@ -1948,7 +1993,6 @@
           <t>Column Notes</t>
         </is>
       </c>
-      <c r="B1" s="36" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1"/>
     <row r="3" ht="26" customHeight="1">
@@ -2050,7 +2094,7 @@
           <t>Client</t>
         </is>
       </c>
-      <c r="B12" s="64" t="n"/>
+      <c r="B12" s="24" t="n"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="62" t="inlineStr">
@@ -2127,7 +2171,7 @@
           <t>• Companion document: Thornfield FY2025 Standalone covering the acquirer's full-year standalone figure.</t>
         </is>
       </c>
-      <c r="B20" s="66" t="n"/>
+      <c r="B20" s="71" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="65" t="inlineStr">
@@ -2135,7 +2179,7 @@
           <t>• Client-level Q4 managed-spend detail: Q4 2025 Managed Spend Export (Grace Feldman).</t>
         </is>
       </c>
-      <c r="B21" s="66" t="n"/>
+      <c r="B21" s="71" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="67" t="inlineStr">
@@ -2143,7 +2187,7 @@
           <t>End of Bramwell FY2025 Standalone.</t>
         </is>
       </c>
-      <c r="B22" s="68" t="n"/>
+      <c r="B22" s="72" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1"/>
     <row r="24" ht="29" customHeight="1"/>
